--- a/docs/Алерты PostgreSQL prod-dp.xlsx
+++ b/docs/Алерты PostgreSQL prod-dp.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Чего мониторинг не видит" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Алерты'!$A$7:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Алерты'!$A$7:$L$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00A61C00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -121,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,15 +139,24 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -509,20 +524,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,14 +558,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Заполнять нужно только жёлтые колонки: нужен ли алерт, какой порог поставить вместо текущего и почему. Остальные колонки описывают, как настроено сейчас.</t>
+          <t>Заполнять нужно только жёлтые колонки: нужна ли проверка, какой порог поставить вместо текущего и почему. Остальное описывает, как настроено сейчас.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Всего правил: 15, из них критичных: 4</t>
+          <t>Проверок: 14, из них критичных: 4. Правил в Grafana: 23 — три проверки заведены отдельно на каждый хост, потому что ходят прямо в базу.</t>
         </is>
       </c>
     </row>
@@ -561,7 +577,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Название в Telegram</t>
+          <t>Проверка</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -586,25 +602,30 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
+          <t>Правил в Grafana</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>Что это значит</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Что делаем при срабатывании</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Нужен? (да / нет)</t>
-        </is>
-      </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
+          <t>Нужна? (да / нет)</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
           <t>Новый порог</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -627,23 +648,24 @@
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>5 минут</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>2 минуты мало, дежурный не успевает посмотреть</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="56" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>1</v>
       </c>
@@ -652,41 +674,44 @@
           <t>БазаНеОтвечает</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>База не отвечает на запросы</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>нет ответа</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>10 секунд</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Приложения, работающие с этой базой, остановлены.</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Поднимаем дежурного, разбираемся на хосте.</t>
         </is>
       </c>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>2</v>
       </c>
@@ -695,41 +720,44 @@
           <t>МониторингОслеп</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Перестали поступать метрики с хоста</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>нет данных</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>1 минута</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>предупреждение</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>Состояние базы неизвестно. Сама база может быть жива, но все остальные проверки в это время слепы.</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Состояние базы неизвестно. Сама база может быть жива, но остальные проверки в это время слепы.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Проверяем сборщик метрик и сеть до хоста.</t>
         </is>
       </c>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>3</v>
       </c>
@@ -738,41 +766,44 @@
           <t>СлотыПодключенийНаИсходе</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Занято больше 80% допустимых подключений</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>5 минут</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>предупреждение</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Запас подключений кончается. Когда дойдёт до предела, новые клиенты начнут получать отказ.</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Смотрим, кто занял: пул приложения или зависшие сессии.</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="52" customHeight="1">
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>4</v>
       </c>
@@ -781,41 +812,44 @@
           <t>СлотыПодключенийИсчерпаны</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Занято больше 95% допустимых подключений</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>1 минута</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Часть клиентов уже получает отказ в подключении.</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Снимаем зависшие сессии, разбираемся с настройками пула.</t>
         </is>
       </c>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1">
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>5</v>
       </c>
@@ -824,477 +858,465 @@
           <t>ЗависшаяIdleInTransaction</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Приложение открыло транзакцию и не закрывает её</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>2 минуты</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>1 минута</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>сразу по достижении порога</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>предупреждение</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Пока транзакция открыта, база не может убирать устаревшие данные: таблицы пухнут, запросы замедляются, растёт расход диска. Эффект накапливается.</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Находим сессию, передаём владельцу приложения.</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
-    </row>
-    <row r="14" ht="52" customHeight="1">
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>В уведомлении видно сессию, пользователя, задачу и сам запрос. Передаём владельцу приложения.</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>ДолгаяТранзакцияDbp2</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Запрос клиента выполняется дольше порога (только dwh-dbp2-lp2)</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>1 минута</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>1 минута</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+          <t>ДолгаяТранзакция</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Запрос клиента выполняется дольше порога</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>1 минута на dwh-dbp2-lp2,
+60 минут на остальных трёх</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>сразу по достижении порога</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>предупреждение</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>Либо тяжёлый отчёт, либо запрос, который сам не завершится. Для базы последствия те же, что в строке 5.</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>Смотрим, что за задача; при необходимости снимаем.</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
+      <c r="G14" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Либо тяжёлый расчёт, либо запрос, который сам не завершится. Для базы последствия те же, что в строке 5.</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>В уведомлении виден текст запроса и задача. Решаем, ждать или снимать.</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>ДолгаяТранзакция</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>То же, для остальных трёх хостов</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>60 минут</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>1 минута</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+          <t>СессииЖдутБлокировку</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Запросы стоят в очереди за данными, занятыми другой транзакцией</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>2 минуты ожидания</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>сразу по достижении порога</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>предупреждение</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>То же, что в строке 6. Порог выше, потому что на этих хостах долгие расчёты в порядке вещей.</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Смотрим, что за задача; при необходимости снимаем.</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
+      <c r="G15" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>Часть работы встала и не двигается, пока блокировка не снимется.</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>В уведомлении видно обе стороны: кто ждёт и кто держит. Разбираем держащего.</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="n"/>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>СессииЖдутБлокировку</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Запросы стоят в очереди за данными, занятыми другой транзакцией</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>1 сессия</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>2 минуты</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+          <t>Взаимоблокировки</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Две транзакции заблокировали друг друга</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>1 случай за 10 минут</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>сразу</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>предупреждение</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Часть работы встала и не двигается, пока блокировка не снимется.</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>Находим, кто кого держит. Требует доступа в базу.</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
+      <c r="G16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>База принудительно откатила одну из них. Приложение получило ошибку, работа потеряна.</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>Разбираем по журналу базы: в метриках только факт, без подробностей.</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="n"/>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Взаимоблокировки</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Две транзакции заблокировали друг друга</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>1 случай за 10 минут</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>сразу</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+          <t>ЗагрузкаCPU</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Процессор хоста занят непрерывно</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>15 минут</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>предупреждение</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>База принудительно откатила одну из них. Приложение получило ошибку, работа потеряна.</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Разбираем по журналу базы.</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="52" customHeight="1">
+      <c r="G17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>Возможны замедления. На хранилище данных во время загрузки это бывает нормой, поэтому порог держится 15 минут.</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Смотрим, что грузит: запросы или ожидание диска.</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ЗагрузкаCPU</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Процессор хоста занят непрерывно</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+          <t>ДискБазыКончается</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Том с данными или журналом заполняется</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>15 минут</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>предупреждение</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Возможны замедления. На хранилище данных во время загрузки это бывает нормой, поэтому порог держится 15 минут.</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Смотрим, что грузит: запросы или ожидание диска.</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>5 минут</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>критично</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>При заполнении до конца база мгновенно прекращает запись. Это не замедление, а остановка.</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Чистим или расширяем том.</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
       <c r="A19" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>ДискБазыКончается</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Том с данными или журналом заполняется</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>5 минут</t>
+          <t>ЗадержкаДискаЧтение</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Хранилище читает медленнее нормы</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>20 мс на операцию</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>10 минут</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>критично</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>При заполнении до конца база мгновенно прекращает запись. Это не замедление, а остановка.</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Чистим или расширяем том.</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
+          <t>предупреждение</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Замедляется всё, что работает с базой. Причина обычно вне базы: хранилище или соседи по массиву.</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Передаём инфраструктуре.</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
       <c r="A20" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ЗадержкаДискаЧтение</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Хранилище читает медленнее нормы</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
+          <t>ЗадержкаДискаЗапись</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Хранилище пишет медленнее нормы</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>20 мс на операцию</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>10 минут</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>предупреждение</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Замедляется всё, что работает с базой. Причина обычно вне базы: хранилище или соседи по массиву.</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="G20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Бьёт сильнее, чем медленное чтение: на записи стоит подтверждение транзакций.</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>Передаём инфраструктуре.</t>
         </is>
       </c>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="52" customHeight="1">
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
       <c r="A21" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>ЗадержкаДискаЗапись</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Хранилище пишет медленнее нормы</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>20 мс на операцию</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
+          <t>МедленноеЧтениеБлоков</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>База ждёт диск дольше нормы</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>5 мс на блок</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>10 минут</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>предупреждение</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Бьёт сильнее, чем медленное чтение: на записи стоит подтверждение транзакций.</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Передаём инфраструктуре.</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
+      <c r="G21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>То же, но измерено со стороны базы: сюда попадает и ситуация, когда данные перестали помещаться в память.</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Смотрим вместе со строками 11-12. Если те молчат, дело в памяти, а не в железе.</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
       <c r="A22" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>МедленноеЧтениеБлоков</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>База ждёт диск дольше нормы</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>5 мс на блок</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>10 минут</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>предупреждение</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>То же, но измерено со стороны базы: сюда попадает и ситуация, когда данные перестали помещаться в память.</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Смотрим вместе со строками 12-13. Если те молчат, дело в памяти, а не в железе.</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
           <t>ОтставаниеРеплики</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Резервная копия базы отстаёт от основной</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>60 секунд</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>1 минута</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>критично</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>При аварийном переключении потеряются данные за время отставания.</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Разбираемся, почему реплика не успевает.</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="10" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:K23"/>
+  <autoFilter ref="A7:L22"/>
   <mergeCells count="4">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A5:L5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1306,7 +1328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1346,70 +1368,87 @@
       </c>
     </row>
     <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Отказы в подключении по причинам, кроме нехватки слотов: неверный пароль, запрет по адресу, проблемы с сертификатом</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>PostgreSQL не ведёт такой счётчик и не отдаёт его наружу ни в одной версии. Нехватка слотов при этом отслеживается, строки 3 и 4.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Сбор и разбор журналов базы. Отдельная работа, к текущим правилам не относится.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Время отклика в процентилях (p95 / p99)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Источники метрик отдают только суммарное время и количество операций. Из них считается среднее, и ничего кроме среднего. Среднее видит устойчивое ухудшение, но не отдельные долгие запросы.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Либо измерение на стороне приложения, либо включение расширенной статистики запросов на хостах баз.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Полностью оборванная репликация</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>При обрыве отставание читается как ноль, и сломанная реплика выглядит здоровой. Правило на этот случай подготовлено, но включать его надо осознанно: на базах с ночным затишьем оно будет срабатывать ложно.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Решение, что для нас дороже: ложные срабатывания по ночам или риск не заметить обрыв.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Текст зависшего запроса и подробности взаимоблокировок</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>В метриках этого нет: данные приходят уже обобщёнными, без текстов запросов и идентификаторов сессий. Сейчас в оповещении видно хост, базу, пользователя и задачу, но не сам запрос.</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Доступ только на чтение к базам со стороны Grafana. Запрошен у администраторов.</t>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Подробности взаимоблокировок: какие именно транзакции схлестнулись</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Метрика даёт только факт и количество. Разбор пишется в журнал базы и больше никуда.</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Сбор журналов. Та же работа, что и в первой строке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Что происходило в прошлом: разбор задним числом</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Строки 5-7 спрашивают базу напрямую и показывают только текущее состояние. Если ночью транзакция повисела и закрылась, утром узнать, что это было, уже нельзя. Метрики историю хранят, прямые запросы — нет.</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Включить на хостах запись в журнал долгих запросов и ожиданий блокировок. Делается одной настройкой без перезапуска базы.</t>
         </is>
       </c>
     </row>
